--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20232.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,106 +82,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>ATENOGENES</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
     <t>RICARDO</t>
   </si>
   <si>
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
-  </si>
-  <si>
     <t>XIMENA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
   </si>
 </sst>
 </file>
@@ -751,16 +709,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>73.08</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -774,16 +735,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -797,16 +761,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -820,16 +787,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -843,16 +813,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -908,16 +881,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>69.23</v>
+        <v>73.08</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -934,16 +907,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>71.88</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -969,7 +942,7 @@
         <v>93.33</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1012,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1086,16 +1059,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920022</v>
+        <v>21330051920023</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1109,22 +1082,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920023</v>
+        <v>21330051920107</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1132,68 +1105,68 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920100</v>
+        <v>20330051920078</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920013</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920078</v>
+        <v>21330051920100</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1201,162 +1174,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920160</v>
+        <v>21330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920012</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920071</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920387</v>
-      </c>
-      <c r="B12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920065</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920139</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20232.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,64 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TENTZOHUA</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>LEON</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>RUBI</t>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>DULIAM</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -641,7 +599,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -650,13 +608,13 @@
         <v>6</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -819,13 +777,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -881,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>25</v>
+      </c>
+      <c r="G2">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H2">
         <v>7</v>
-      </c>
-      <c r="F2">
-        <v>19</v>
-      </c>
-      <c r="G2">
-        <v>73.08</v>
-      </c>
-      <c r="H2">
-        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -907,13 +865,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>96.88</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -942,7 +900,7 @@
         <v>93.33</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -959,13 +917,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -979,22 +937,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1036,22 +994,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920022</v>
+        <v>21330051920109</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1059,7 +1017,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920023</v>
+        <v>20330051920078</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -1068,7 +1026,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1077,121 +1035,6 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920107</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920078</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920013</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920065</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>
